--- a/同位素杂质计算/sp_003_杂质含量.xlsx
+++ b/同位素杂质计算/sp_003_杂质含量.xlsx
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>不带电荷分子量</t>
+          <t>不带电荷单同位素质量</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>不带电荷分子量</t>
+          <t>不带电荷单同位素质量</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
